--- a/dados_profiles.xlsx
+++ b/dados_profiles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">ID usuario</t>
   </si>
@@ -34,6 +34,9 @@
     <t xml:space="preserve">username</t>
   </si>
   <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Token</t>
   </si>
   <si>
@@ -49,7 +52,7 @@
     <t xml:space="preserve">agente_performance_bot</t>
   </si>
   <si>
-    <t xml:space="preserve">8860834193:AAFRslNCtktySk-9uW3BegCQa4exwoOz3EM</t>
+    <t xml:space="preserve">time-performance</t>
   </si>
   <si>
     <t xml:space="preserve">Agente Pedagógico</t>
@@ -58,7 +61,7 @@
     <t xml:space="preserve">agente_pedagogico_bot</t>
   </si>
   <si>
-    <t xml:space="preserve">8424962468:AAEnSVg689-ssbeGdjMYdZfxhpEGYCjVejo</t>
+    <t xml:space="preserve">time-pedagogico</t>
   </si>
   <si>
     <t xml:space="preserve">Agente de CS</t>
@@ -67,7 +70,7 @@
     <t xml:space="preserve">agente_custer_service_bot</t>
   </si>
   <si>
-    <t xml:space="preserve">8171565546:AAEM2rOCWKbLw_zQaN0f_YsVPOu5xvDz-iU</t>
+    <t xml:space="preserve">time-cs</t>
   </si>
   <si>
     <t xml:space="preserve">Agente Comercial</t>
@@ -76,7 +79,7 @@
     <t xml:space="preserve">agente_comercial_bot</t>
   </si>
   <si>
-    <t xml:space="preserve">8877286437:AAFkX5PYYoraqkviW6QY2Kq0K_tKsfXeRmQ</t>
+    <t xml:space="preserve">time-comercial</t>
   </si>
   <si>
     <t xml:space="preserve">Agente de Conteúdo</t>
@@ -85,21 +88,23 @@
     <t xml:space="preserve">agente_conteudo_bot</t>
   </si>
   <si>
-    <t xml:space="preserve">8540012178:AAFd01UFeoPriAwNeZ1nfyzqV9IOr-7MEdA</t>
+    <t xml:space="preserve">time-conteudo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -121,6 +126,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -171,13 +177,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -363,98 +377,99 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="49.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.25"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="n">
-        <v>758543036</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D7" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dados_profiles.xlsx
+++ b/dados_profiles.xlsx
@@ -20,9 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t xml:space="preserve">ID usuario</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t xml:space="preserve">ID usuario-Telegram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELEGRAM_ALLOWED_USERS</t>
   </si>
   <si>
     <t xml:space="preserve">Bot name</t>
@@ -31,64 +34,22 @@
     <t xml:space="preserve">Descrição (opcional)</t>
   </si>
   <si>
-    <t xml:space="preserve">username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
+    <t xml:space="preserve">Username</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile</t>
   </si>
   <si>
     <t xml:space="preserve">Token</t>
   </si>
   <si>
-    <t xml:space="preserve">Agente CTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agente_cto_bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agente de Performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agente_performance_bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">time-performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agente Pedagógico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agente_pedagogico_bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">time-pedagogico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agente de CS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agente_custer_service_bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">time-cs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agente Comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agente_comercial_bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">time-comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agente de Conteúdo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agente_conteudo_bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">time-conteudo</t>
+    <t xml:space="preserve">TELEGRAM_HOME_CHANNEL_NAME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELEGRAM_BOT_TOKEN</t>
   </si>
 </sst>
 </file>
@@ -99,7 +60,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -127,6 +88,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -177,7 +144,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -187,6 +154,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -377,102 +352,77 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:B2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
